--- a/output/pdf_financials_xlsx/KIB.xlsx
+++ b/output/pdf_financials_xlsx/KIB.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.974595</v>
+        <v>-0.974595</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4.576276</v>
+        <v>-4.576276</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.502302</v>
+        <v>-1.502302</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.131036</v>
+        <v>-0.131036</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.10003</v>
+        <v>-0.10003</v>
       </c>
     </row>
     <row r="17">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.974595</v>
+        <v>-0.974595</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.576276</v>
+        <v>-4.576276</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.502302</v>
+        <v>-1.502302</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.131036</v>
+        <v>-0.131036</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.10003</v>
+        <v>-0.10003</v>
       </c>
     </row>
     <row r="21">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.974595</v>
+        <v>-0.974595</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4.576276</v>
+        <v>-4.576276</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.502302</v>
+        <v>-1.502302</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.131036</v>
+        <v>-0.131036</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.10003</v>
+        <v>-0.10003</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>13.922786</v>
+        <v>-13.922786</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>28.601725</v>
+        <v>-28.601725</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>50.076733</v>
+        <v>-50.076733</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>4.367867</v>
+        <v>-4.367867</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5.0015</v>
+        <v>-5.0015</v>
       </c>
     </row>
     <row r="27">
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.974595</v>
+        <v>-0.974595</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4.576276</v>
+        <v>-4.576276</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.502302</v>
+        <v>-1.502302</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.131036</v>
+        <v>-0.131036</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.10003</v>
+        <v>-0.10003</v>
       </c>
     </row>
     <row r="28">
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.974595</v>
+        <v>-0.974595</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4.576276</v>
+        <v>-4.576276</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.502302</v>
+        <v>-1.502302</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.131036</v>
+        <v>-0.131036</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.10003</v>
+        <v>-0.10003</v>
       </c>
     </row>
     <row r="30">
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -8068,19 +8068,19 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0.974595</v>
+        <v>-0.974595</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>4.576276</v>
+        <v>-4.576276</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1.502302</v>
+        <v>-1.502302</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>0.131036</v>
+        <v>-0.131036</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>0.10003</v>
+        <v>-0.10003</v>
       </c>
     </row>
     <row r="114">

--- a/output/pdf_financials_xlsx/KIB.xlsx
+++ b/output/pdf_financials_xlsx/KIB.xlsx
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000228</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.046184</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.017904</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000835</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.974595</v>
+        <v>-0.974367</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.576276</v>
+        <v>-4.530092</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.502302</v>
+        <v>-1.484398</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.131036</v>
+        <v>-0.130201</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.10003</v>
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.974595</v>
+        <v>-0.974367</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.576276</v>
+        <v>-4.530092</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.502302</v>
+        <v>-1.484398</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.131036</v>
+        <v>-0.130201</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.10003</v>
@@ -1187,10 +1187,10 @@
         <v>0.176735</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.026282</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.011173</v>
       </c>
     </row>
     <row r="35">
@@ -1231,10 +1231,10 @@
         <v>0.176735</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.026282</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.011173</v>
       </c>
     </row>
     <row r="37">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">

--- a/output/pdf_financials_xlsx/KIB.xlsx
+++ b/output/pdf_financials_xlsx/KIB.xlsx
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.017434</v>
+        <v>0.019968</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.106716</v>
+        <v>0.109354</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.165512</v>
+        <v>0.187715</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.002083</v>
+        <v>0.004947</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>0.002543</v>
       </c>
     </row>
     <row r="8">
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.439666</v>
+        <v>0.4422</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.319325</v>
+        <v>0.321963</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.189417</v>
+        <v>0.21162</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.025633</v>
+        <v>0.028497</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.029318</v>
+        <v>0.031861</v>
       </c>
     </row>
     <row r="11">
@@ -7801,7 +7801,11 @@
           <t>Office expense</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E106" s="5" t="n">
         <v>0.002534</v>
       </c>
